--- a/input/PL/reg_wages.xlsx
+++ b/input/PL/reg_wages.xlsx
@@ -17,24 +17,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="194" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="204" uniqueCount="46">
   <si>
-    <t>Description:</t>
-  </si>
-  <si>
-    <t>This file contains regression estimates used to calculate potential wages for males and females in the simulation.</t>
+    <t>Description</t>
   </si>
   <si>
     <t>Authors:</t>
   </si>
   <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
     <t>Last edit:</t>
   </si>
   <si>
-    <t>12 Jan 2016 AB</t>
+    <t/>
   </si>
   <si>
     <t>Process:</t>
@@ -43,28 +37,40 @@
     <t>W1fa</t>
   </si>
   <si>
-    <t>Heckman selection estimates using women that do not have an observed wage in the previous year</t>
+    <t>W1ma</t>
   </si>
   <si>
-    <t>W1ma</t>
+    <t>W1fb</t>
+  </si>
+  <si>
+    <t>W1mb</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Thisfilecontainsregressiones</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
+  <si>
+    <t>Description:</t>
+  </si>
+  <si>
+    <t>Heckman selection estimates using women that do not have an observed wage in the previous year</t>
   </si>
   <si>
     <t>Heckman selection estimates using men that do not have an observed wage in the previous year</t>
   </si>
   <si>
-    <t>W1fb</t>
-  </si>
-  <si>
     <t>Heckman selection estimates using women that have an observed wage in the previous year</t>
   </si>
   <si>
-    <t>W1mb</t>
-  </si>
-  <si>
     <t>Heckman selection estimates using men that have an observed wage in the previous year</t>
-  </si>
-  <si>
-    <t>Notes:</t>
   </si>
   <si>
     <t>Estimated on panel data unlike the labour supply estimates</t>
@@ -83,9 +89,6 @@
   </si>
   <si>
     <t>REGRESSOR</t>
-  </si>
-  <si>
-    <t>COEFFICIENT</t>
   </si>
   <si>
     <t>Dag</t>
@@ -148,6 +151,9 @@
     <t>InverseMillsRatio</t>
   </si>
   <si>
+    <t>COEFFICIENT</t>
+  </si>
+  <si>
     <t>L1_log_hourly_wage</t>
   </si>
 </sst>
@@ -155,64 +161,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="13">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -223,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -231,78 +183,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -316,95 +204,131 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>15</v>
+      <c r="A12" t="s">
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -418,1429 +342,1429 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.02756038512254512</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>3.9094177683009477e-06</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-4.3412326364412126e-08</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>9.105093855408788e-06</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>5.6229781266145595e-06</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-2.1262250326001316e-07</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-1.2892575992729728e-07</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>1.7047170378650704e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>6.5060436615116671e-07</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>6.4852851999780335e-07</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>2.7561641555293622e-06</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>1.3143179693236634e-07</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>3.3450925893121368e-07</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-1.1793200456138481e-07</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>9.9041333217627629e-08</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>1.2789948781376988e-06</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-3.4375341952154892e-09</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-1.058001412795605e-08</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-3.5358766459058655e-08</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-8.4678763794249884e-05</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>5.5015500981690754e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.00014709445492865899</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-4.3412326364412126e-08</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>5.073179342493349e-10</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-1.8954015180947943e-08</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>2.2590732340977448e-08</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>3.3890972149988335e-10</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-6.4722842199709239e-10</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-3.2817282589297645e-09</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-8.8585717538679645e-09</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-4.9348322674383209e-09</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>-2.3040131723797924e-08</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>-2.2228037403188392e-09</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-4.4417432093668868e-09</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>4.8382938488878094e-10</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-1.6118211789132648e-09</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-1.6318463915393442e-08</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-8.2275943349628504e-11</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>1.0888333183137416e-09</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>1.6521049162121089e-09</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>9.0774203288377429e-07</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-6.4010883306259773e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
         <v>-0.052945417572707473</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>9.105093855408788e-06</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-1.8954015180947943e-08</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.00054094256734251529</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.00033066776812605325</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-1.2131496339305986e-05</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-7.5701178124334009e-06</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-2.8623670983213158e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-7.2750791608983079e-06</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-1.163655889840385e-05</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-4.1931337227213907e-06</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-4.4933483227089712e-06</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-2.1193613503782477e-07</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-4.2810659187460961e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>5.4805204834898033e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-2.6367203142139981e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>1.7770443751060467e-08</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>1.19929931032449e-06</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>1.8238519895441664e-06</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-0.00034570616960644118</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>-8.3208636249703199e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.027725141301688194</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>5.6229781266145595e-06</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2.2590732340977448e-08</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.00033066776812605325</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.0026814102523067622</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-7.6037447818725018e-06</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-5.5039503825814367e-05</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>-1.9399140753782004e-06</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-1.8133234629499671e-05</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-2.5739766420804783e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-1.4031843443065687e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-1.1056039544491393e-05</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-2.9637349998552501e-06</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-7.2967913720472295e-06</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>8.1130829709934965e-07</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-4.6145860938255099e-06</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-2.0937434801053476e-07</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>4.0034149529858368e-06</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>4.0873688734101699e-06</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-0.00023227824312207574</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-3.7278452635691052e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.0094202005876875081</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-2.1262250326001316e-07</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>3.3890972149988335e-10</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-1.2131496339305986e-05</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-7.6037447818725018e-06</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>2.9044490167754614e-07</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1.8660306509228243e-07</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>1.1472133975131217e-08</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>1.1821241899640385e-07</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>2.8760632332145093e-07</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1.806645530169057e-07</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>8.0848123575577238e-08</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>2.1579970699855893e-08</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>9.5146900621161904e-08</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>1.4022960420828322e-08</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>1.0918417767728896e-07</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>2.9770115306044985e-09</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-4.6016727656604082e-08</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-6.7083111472997357e-08</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>7.4210732011730934e-06</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>9.603104021813766e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.013332777787543068</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-1.2892575992729728e-07</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-6.4722842199709239e-10</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-7.5701178124334009e-06</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-5.5039503825814367e-05</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>1.8660306509228243e-07</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>1.2111842843504121e-06</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>2.7583804845489473e-07</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>6.7452726289586954e-07</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>1.0050641348471037e-06</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>8.2076643754166005e-07</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>1.2507762089165025e-07</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>6.5617958409142476e-08</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>5.4492532791324484e-08</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>-4.7455561765246345e-08</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>6.5603796827807944e-08</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>9.782328232349108e-09</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-1.1480004107628295e-07</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-1.2024347342175226e-07</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>4.276049124210138e-06</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>5.1117242884407014e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
         <v>0.14521720804520419</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1.7047170378650704e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-3.2817282589297645e-09</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-2.8623670983213158e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>-1.9399140753782004e-06</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>1.1472133975131217e-08</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>2.7583804845489473e-07</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.0032117221865465679</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.0029721820667199007</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0.0029727213926968787</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>0.0029718508664808548</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>1.1029743346468892e-06</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>-1.3734562945579666e-06</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-3.6034730114200101e-06</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>-1.2409328562350466e-06</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-3.4832613460509672e-06</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>1.0191582436972614e-07</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>-2.644325186828659e-06</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-1.7874741981740263e-06</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-0.0029858144801558953</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>1.4272935594146947e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.1778331518300503</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>6.5060436615116671e-07</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-8.8585717538679645e-09</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-7.2750791608983079e-06</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-1.8133234629499671e-05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>1.1821241899640385e-07</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>6.7452726289586954e-07</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.0029721820667199007</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0030118635998372259</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.0029783280011125794</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.0029779733741731127</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>5.0802378892008122e-07</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>-9.1916896192658944e-07</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-3.9006392202693454e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-1.7537730642518487e-06</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-1.9793319739739495e-06</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>8.8856372095885411e-08</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>-3.3881485313155509e-06</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-1.9612711074092593e-06</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-0.0030018474625094875</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>2.3661914078681195e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.23122808410346091</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>6.4852851999780335e-07</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-4.9348322674383209e-09</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-1.163655889840385e-05</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-2.5739766420804783e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>2.8760632332145093e-07</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>1.0050641348471037e-06</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>0.0029727213926968787</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.0029783280011125794</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0029969055631230055</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0029871980615279281</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>1.1049853472997656e-07</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>-1.1425656982258928e-06</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-4.2677320195136374e-06</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-1.1721539861727038e-06</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>-5.3887056103366943e-07</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-1.1914094441330043e-08</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-3.4198875170717361e-06</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>-2.4380416845731332e-06</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-0.003007071827024357</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>2.6885965366010445e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.27428977449831826</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>2.7561641555293622e-06</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-2.3040131723797924e-08</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-4.1931337227213907e-06</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-1.4031843443065687e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>1.806645530169057e-07</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>8.2076643754166005e-07</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>0.0029718508664808548</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.0029779733741731127</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0029871980615279281</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0030375222930679869</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>1.3191060894607645e-06</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>2.010514677780871e-07</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-4.0900127107802829e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>4.419328190105563e-07</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-4.2612429209558053e-07</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-6.513471440092746e-09</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-3.7731980333074574e-06</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-3.0421058811331884e-06</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-0.0030682223206207689</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>2.7876423221100447e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.0035354220285032786</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1.3143179693236634e-07</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-2.2228037403188392e-09</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-4.4933483227089712e-06</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-1.1056039544491393e-05</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>8.0848123575577238e-08</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>1.2507762089165025e-07</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1.1029743346468892e-06</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>5.0802378892008122e-07</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>1.1049853472997656e-07</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>1.3191060894607645e-06</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>9.0866851603560165e-05</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>4.394413143299651e-05</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>4.4117986438830059e-05</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>4.4002678000471944e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>2.1113987167205292e-06</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-8.5695456835984422e-08</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-3.8602252927837047e-07</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-8.5642329685827697e-07</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-3.6009715422119075e-05</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>1.4374284900879872e-06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.028132375615882794</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>3.3450925893121368e-07</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-4.4417432093668868e-09</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-2.1193613503782477e-07</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-2.9637349998552501e-06</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>2.1579970699855893e-08</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>6.5617958409142476e-08</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-1.3734562945579666e-06</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>-9.1916896192658944e-07</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>-1.1425656982258928e-06</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>2.010514677780871e-07</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>4.394413143299651e-05</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.00011844385125413499</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>4.3908200868048791e-05</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>4.3955978714466854e-05</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>1.6389254451907835e-06</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-4.6232127080230363e-08</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-1.4004272175010966e-06</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-9.1100256641412863e-07</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-4.4028069676584875e-05</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>1.765249295423608e-08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.0030285314102534732</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-1.1793200456138481e-07</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>4.8382938488878094e-10</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>-4.2810659187460961e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-7.2967913720472295e-06</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>9.5146900621161904e-08</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>5.4492532791324484e-08</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-3.6034730114200101e-06</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-3.9006392202693454e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-4.2677320195136374e-06</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-4.0900127107802829e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>4.4117986438830059e-05</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>4.3908200868048791e-05</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>9.0365854557603371e-05</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>4.3970974997879376e-05</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>1.40851222117042e-06</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-9.3763076205328928e-08</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>1.8692087883774607e-07</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>4.0812259491188154e-07</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-2.51788358570416e-05</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-5.3359949809784304e-07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.046379525985056597</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>9.9041333217627629e-08</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-1.6118211789132648e-09</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>5.4805204834898033e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>8.1130829709934965e-07</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>1.4022960420828322e-08</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>-4.7455561765246345e-08</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>-1.2409328562350466e-06</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-1.7537730642518487e-06</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-1.1721539861727038e-06</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>4.419328190105563e-07</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>4.4002678000471944e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>4.3955978714466854e-05</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>4.3970974997879376e-05</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>6.1746621737586573e-05</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>1.3874459521720712e-06</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-6.100311137914845e-08</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-1.0328563551309907e-06</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-8.0640729136824493e-07</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-3.8099493062989189e-05</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>5.818286220634012e-07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.15982527739376395</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>1.2789948781376988e-06</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-1.6318463915393442e-08</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-2.6367203142139981e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-4.6145860938255099e-06</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>1.0918417767728896e-07</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>6.5603796827807944e-08</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-3.4832613460509672e-06</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-1.9793319739739495e-06</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-5.3887056103366943e-07</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-4.2612429209558053e-07</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>2.1113987167205292e-06</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>1.6389254451907835e-06</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>1.40851222117042e-06</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>1.3874459521720712e-06</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.00010228193007585179</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>1.1815454556758731e-07</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>-1.0588764121324807e-06</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-1.2603227250518295e-06</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-4.3820083317784337e-05</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-5.7653275265070218e-06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.0040327026175400746</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-3.4375341952154892e-09</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-8.2275943349628504e-11</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>1.7770443751060467e-08</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-2.0937434801053476e-07</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>2.9770115306044985e-09</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>9.782328232349108e-09</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>1.0191582436972614e-07</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>8.8856372095885411e-08</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-1.1914094441330043e-08</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-6.513471440092746e-09</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-8.5695456835984422e-08</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-4.6232127080230363e-08</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-9.3763076205328928e-08</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-6.100311137914845e-08</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>1.1815454556758731e-07</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>5.0660645108179331e-08</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>-7.6818375371094519e-07</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-9.2609302246392652e-07</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-5.1952909857464095e-06</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-7.9525746318824808e-09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.051344189731201063</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-1.058001412795605e-08</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>1.0888333183137416e-09</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>1.19929931032449e-06</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>4.0034149529858368e-06</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-4.6016727656604082e-08</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-1.1480004107628295e-07</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>-2.644325186828659e-06</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>-3.3881485313155509e-06</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-3.4198875170717361e-06</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-3.7731980333074574e-06</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-3.8602252927837047e-07</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-1.4004272175010966e-06</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>1.8692087883774607e-07</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-1.0328563551309907e-06</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>-1.0588764121324807e-06</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>-7.6818375371094519e-07</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.00013317542884041104</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>2.2766731362217653e-05</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>7.7534171072777777e-05</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-1.7122668301317903e-06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.025676926152059697</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-3.5358766459058655e-08</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>1.6521049162121089e-09</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>1.8238519895441664e-06</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>4.0873688734101699e-06</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>-6.7083111472997357e-08</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-1.2024347342175226e-07</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-1.7874741981740263e-06</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-1.9612711074092593e-06</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>-2.4380416845731332e-06</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-3.0421058811331884e-06</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-8.5642329685827697e-07</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-9.1100256641412863e-07</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>4.0812259491188154e-07</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-8.0640729136824493e-07</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-1.2603227250518295e-06</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-9.2609302246392652e-07</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>2.2766731362217653e-05</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.00014764942521231788</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>9.3171971986183604e-05</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-3.8284543933049393e-07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1">
         <v>0.097727936411406452</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-8.4678763794249884e-05</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>9.0774203288377429e-07</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-0.00034570616960644118</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-0.00023227824312207574</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>7.4210732011730934e-06</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>4.276049124210138e-06</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-0.0029858144801558953</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-0.0030018474625094875</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-0.003007071827024357</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-0.0030682223206207689</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-3.6009715422119075e-05</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-4.4028069676584875e-05</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-2.51788358570416e-05</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-3.8099493062989189e-05</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-4.3820083317784337e-05</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-5.1952909857464095e-06</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>7.7534171072777777e-05</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>9.3171971986183604e-05</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0055121223603009578</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-0.00014923471383976647</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1">
         <v>-0.12278272809955822</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>5.5015500981690754e-06</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-6.4010883306259773e-08</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>-8.3208636249703199e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-3.7278452635691052e-05</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>9.603104021813766e-08</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>5.1117242884407014e-07</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>1.4272935594146947e-05</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>2.3661914078681195e-05</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>2.6885965366010445e-05</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>2.7876423221100447e-05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>1.4374284900879872e-06</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>1.765249295423608e-08</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-5.3359949809784304e-07</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>5.818286220634012e-07</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-5.7653275265070218e-06</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-7.9525746318824808e-09</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-1.7122668301317903e-06</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-3.8284543933049393e-07</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-0.00014923471383976647</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>6.3409686886901635e-05</v>
       </c>
     </row>
@@ -1855,1429 +1779,1429 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.044089990906754667</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>3.1867423585891767e-06</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-3.3422527549098914e-08</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>1.4734753069432241e-05</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>1.4732025391733055e-05</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-3.3702457312999881e-07</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>-3.2906755748787203e-07</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>9.0027091702929902e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>1.7350870213164091e-06</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>1.3573654014171725e-06</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>3.1237034757533522e-06</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>1.2865829792068567e-07</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-8.290945033152623e-08</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-1.8034584854327473e-07</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-3.2476636086116076e-08</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>2.5097470072747765e-06</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>3.27532185534478e-09</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-1.1266731643136038e-07</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-4.9240879853158923e-08</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-7.3731207995942046e-05</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>5.8893886140746874e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.0003914687533946434</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-3.3422527549098914e-08</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>3.8301065690921348e-10</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-4.6906374438442382e-08</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-4.4447909603100696e-08</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>8.9744020835153932e-10</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>7.7145536103987517e-10</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-1.0859457316945773e-08</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-2.1163217623042313e-08</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-1.2937055669805024e-08</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>-2.7612490120399593e-08</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>-2.2903265963288873e-09</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-2.4512562667604236e-10</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>1.3176093308278313e-09</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>2.1284369759490852e-10</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-3.2168543603014036e-08</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-1.2793700946584175e-10</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>2.8143321361090695e-09</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>1.8476190619147848e-09</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>7.2550329559949283e-07</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-7.1167560079992135e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
         <v>-0.085645505829612001</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1.4734753069432241e-05</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-4.6906374438442382e-08</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.00061118127581049307</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.00047953791160198041</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-1.3682746762943914e-05</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-1.0817532168109481e-05</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>8.9956966152350574e-07</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-3.1326799167532199e-06</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-8.5832009776653968e-06</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-3.610855962458945e-06</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-1.8675330639703881e-06</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-2.206684063610919e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-2.0375967653780276e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>5.2675625398945624e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-2.6942134823599652e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>6.7706743054041105e-08</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>2.8279702943841768e-06</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>1.3555478993435455e-06</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-0.00055339562067209937</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>9.209704830854612e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.028484170061441206</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1.4732025391733055e-05</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-4.4447909603100696e-08</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.00047953791160198041</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.0015424007014252115</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-1.0881025510753709e-05</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-3.3018747800150986e-05</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>-6.9303621608160084e-06</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-2.1362693686191096e-05</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-2.9465630682055805e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-2.2738257595153566e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-9.3847889400198524e-06</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-3.4770510671619711e-06</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-8.0103476375253537e-06</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>2.474907930041001e-06</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-8.1283115546652139e-06</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-1.3509283840810307e-07</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>5.8555779541094059e-06</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>4.135722802435394e-06</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-0.00050680738473842901</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-3.593041920706687e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.0075525313564613478</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-3.3702457312999881e-07</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>8.9744020835153932e-10</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-1.3682746762943914e-05</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>-1.0881025510753709e-05</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>3.3025084732801524e-07</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2.6416330595081034e-07</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-2.4128273844493371e-08</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>9.2937878137867968e-08</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>2.8764045229889442e-07</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>2.3812154380973806e-07</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-1.1271533212305586e-08</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>4.8502059075026164e-08</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>1.3041533963236109e-08</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-1.827038358448061e-08</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>1.5154266251446374e-07</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>1.0547750081845717e-09</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-8.515285910345798e-08</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-6.0848716315143154e-08</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>1.183622281028206e-05</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>5.8527564824382273e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.015328325942405966</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>-3.2906755748787203e-07</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>7.7145536103987517e-10</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-1.0817532168109481e-05</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-3.3018747800150986e-05</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>2.6416330595081034e-07</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>7.7382390402345466e-07</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>8.1223312941666505e-08</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>3.9880547862181754e-07</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>6.7741377302649228e-07</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>6.1167331372513895e-07</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>1.0901193723437167e-07</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>7.1761002470512731e-08</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>7.4562843319557291e-08</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>-1.2882971880340721e-07</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>1.5114545687967586e-07</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>7.0043202239466088e-09</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-1.5055203404069946e-07</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-1.2711221873758899e-07</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>1.0615374689286819e-05</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>6.4201041184262957e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
         <v>0.00085735653502216338</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>9.0027091702929902e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-1.0859457316945773e-08</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>8.9956966152350574e-07</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>-6.9303621608160084e-06</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-2.4128273844493371e-08</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>8.1223312941666505e-08</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.0025670461223516591</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.0023372449523981244</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0.0023378908362493888</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>0.0023378713719609126</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>1.4157008058790242e-06</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>2.5491747549438782e-06</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-1.6226311133207985e-06</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>-1.3315914736764515e-06</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-1.3321208657684792e-06</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>1.6255112391411201e-07</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>-4.7165307209753442e-06</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-1.2045648035738468e-06</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-0.0023747648316246807</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>1.6049747223289379e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.06764968874866964</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>1.7350870213164091e-06</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-2.1163217623042313e-08</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-3.1326799167532199e-06</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-2.1362693686191096e-05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>9.2937878137867968e-08</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>3.9880547862181754e-07</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.0023372449523981244</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0023832731596328282</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.0023484933936746377</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.0023489910309556468</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>1.0213675397430751e-06</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>2.233620268004244e-06</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-2.9809762964607549e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-2.6183166381003103e-06</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>3.9904361850507612e-06</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>1.1704333449395445e-07</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>-3.8729690351844935e-06</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-1.8391901428901284e-06</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-0.0023992842248120243</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>3.5855343860716778e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.12433430750361178</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>1.3573654014171725e-06</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-1.2937055669805024e-08</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-8.5832009776653968e-06</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-2.9465630682055805e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>2.8764045229889442e-07</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>6.7741377302649228e-07</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>0.0023378908362493888</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.0023484933936746377</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0023700545193529937</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0023613886667990455</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>1.0562947907948954e-06</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>3.1023118104378108e-06</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-2.2567739326149756e-06</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-1.3447333303994167e-06</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>6.7117800353691407e-06</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>2.030935796973752e-08</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-3.7727319387197136e-06</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>-2.0950899475882145e-06</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-0.002401545794902077</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>4.2280945704583337e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.16193639379127778</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>3.1237034757533522e-06</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-2.7612490120399593e-08</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-3.610855962458945e-06</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-2.2738257595153566e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>2.3812154380973806e-07</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>6.1167331372513895e-07</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>0.0023378713719609126</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.0023489910309556468</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0023613886667990455</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0024052048247130628</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>1.2616872794514466e-06</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>3.6326872794877424e-06</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-2.5869885190317281e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-8.9849564948965783e-07</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>6.5324685923825371e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>2.8132974683146984e-08</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-3.931772578733974e-06</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-1.8214751639954965e-06</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-0.002455535618259301</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>4.2818159856695558e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1">
         <v>-0.021158141827239456</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1.2865829792068567e-07</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-2.2903265963288873e-09</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-1.8675330639703881e-06</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-9.3847889400198524e-06</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-1.1271533212305586e-08</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>1.0901193723437167e-07</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1.4157008058790242e-06</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>1.0213675397430751e-06</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>1.0562947907948954e-06</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>1.2616872794514466e-06</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>8.8802361474983797e-05</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>4.3079564120400944e-05</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>4.3209813696747893e-05</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>4.3069821860170472e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>2.4187539503430107e-06</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-8.0047246567186782e-08</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-7.6625999574000823e-07</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-6.1088453259454921e-07</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-3.4816655519078777e-05</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>2.0420411984943325e-06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.06806578630594573</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-8.290945033152623e-08</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-2.4512562667604236e-10</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-2.206684063610919e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-3.4770510671619711e-06</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>4.8502059075026164e-08</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>7.1761002470512731e-08</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>2.5491747549438782e-06</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>2.233620268004244e-06</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>3.1023118104378108e-06</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>3.6326872794877424e-06</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>4.3079564120400944e-05</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.00011576754190557805</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>4.306732035236505e-05</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>4.3031236098917105e-05</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>2.9829949529724065e-06</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-6.3976799824398668e-08</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-1.563100521931325e-06</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-1.0227624580290466e-06</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-3.4727344183492845e-05</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-4.4570792321034281e-07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1">
         <v>-0.017967541798142542</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-1.8034584854327473e-07</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>1.3176093308278313e-09</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>-2.0375967653780276e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-8.0103476375253537e-06</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>1.3041533963236109e-08</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>7.4562843319557291e-08</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-1.6226311133207985e-06</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-2.9809762964607549e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-2.2567739326149756e-06</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-2.5869885190317281e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>4.3209813696747893e-05</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>4.306732035236505e-05</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>8.7308107278910959e-05</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>4.3090078414428741e-05</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>3.215003511757634e-06</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-9.1984689604368023e-08</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-2.2978109561790585e-09</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>5.3301785691581414e-07</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-2.4121723298985642e-05</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>-3.7578114064756865e-07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.095309172267773301</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-3.2476636086116076e-08</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>2.1284369759490852e-10</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>5.2675625398945624e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>2.474907930041001e-06</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-1.827038358448061e-08</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>-1.2882971880340721e-07</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>-1.3315914736764515e-06</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-2.6183166381003103e-06</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-1.3447333303994167e-06</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-8.9849564948965783e-07</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>4.3069821860170472e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>4.3031236098917105e-05</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>4.3090078414428741e-05</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>6.0776496767843795e-05</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>1.3152937669107921e-06</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-6.6601263239540021e-08</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-8.7940541384463716e-07</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-9.594214631731364e-07</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-3.2853503108164767e-05</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>2.7141874191134781e-07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.00023312310254713629</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>2.5097470072747765e-06</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-3.2168543603014036e-08</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-2.6942134823599652e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-8.1283115546652139e-06</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>1.5154266251446374e-07</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>1.5114545687967586e-07</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-1.3321208657684792e-06</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>3.9904361850507612e-06</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>6.7117800353691407e-06</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>6.5324685923825371e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>2.4187539503430107e-06</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>2.9829949529724065e-06</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>3.215003511757634e-06</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>1.3152937669107921e-06</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.00028682395572595401</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>1.166782186738199e-07</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>-1.1570547817457277e-06</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-8.5056560677177631e-07</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-7.1887331795276175e-05</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-1.0633793224383252e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.0051605092250917098</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>3.27532185534478e-09</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-1.2793700946584175e-10</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>6.7706743054041105e-08</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-1.3509283840810307e-07</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>1.0547750081845717e-09</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>7.0043202239466088e-09</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>1.6255112391411201e-07</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>1.1704333449395445e-07</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>2.030935796973752e-08</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>2.8132974683146984e-08</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-8.0047246567186782e-08</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-6.3976799824398668e-08</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-9.1984689604368023e-08</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-6.6601263239540021e-08</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>1.166782186738199e-07</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>4.915188888602816e-08</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>-7.6216923853280521e-07</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-9.1586197032975384e-07</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-5.2473514348186791e-06</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>4.3238910331939366e-08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.044896845491463298</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-1.1266731643136038e-07</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>2.8143321361090695e-09</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>2.8279702943841768e-06</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>5.8555779541094059e-06</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-8.515285910345798e-08</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-1.5055203404069946e-07</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>-4.7165307209753442e-06</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>-3.8729690351844935e-06</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-3.7727319387197136e-06</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-3.931772578733974e-06</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-7.6625999574000823e-07</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-1.563100521931325e-06</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-2.2978109561790585e-09</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-8.7940541384463716e-07</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>-1.1570547817457277e-06</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>-7.6216923853280521e-07</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.00013391315804909873</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>2.265857443922104e-05</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>7.8352288598642025e-05</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-2.1958277495508924e-06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.022192730282062929</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-4.9240879853158923e-08</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>1.8476190619147848e-09</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>1.3555478993435455e-06</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>4.135722802435394e-06</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>-6.0848716315143154e-08</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-1.2711221873758899e-07</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-1.2045648035738468e-06</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-1.8391901428901284e-06</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>-2.0950899475882145e-06</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-1.8214751639954965e-06</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-6.1088453259454921e-07</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-1.0227624580290466e-06</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>5.3301785691581414e-07</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-9.594214631731364e-07</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-8.5056560677177631e-07</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-9.1586197032975384e-07</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>2.265857443922104e-05</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.00014553854911902807</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>9.2073340953292615e-05</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-8.8167121547009105e-07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.032169060389340989</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-7.3731207995942046e-05</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>7.2550329559949283e-07</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-0.00055339562067209937</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-0.00050680738473842901</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>1.183622281028206e-05</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>1.0615374689286819e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-0.0023747648316246807</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-0.0023992842248120243</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-0.002401545794902077</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-0.002455535618259301</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-3.4816655519078777e-05</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-3.4727344183492845e-05</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-2.4121723298985642e-05</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-3.2853503108164767e-05</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-7.1887331795276175e-05</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-5.2473514348186791e-06</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>7.8352288598642025e-05</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>9.2073340953292615e-05</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0047914359583406032</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-0.00017788360939971246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1">
         <v>-0.16908062284592648</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>5.8893886140746874e-06</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-7.1167560079992135e-08</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>9.209704830854612e-07</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-3.593041920706687e-05</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>5.8527564824382273e-08</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>6.4201041184262957e-07</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>1.6049747223289379e-05</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>3.5855343860716778e-05</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>4.2280945704583337e-05</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>4.2818159856695558e-05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>2.0420411984943325e-06</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-4.4570792321034281e-07</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>-3.7578114064756865e-07</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>2.7141874191134781e-07</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-1.0633793224383252e-05</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>4.3238910331939366e-08</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-2.1958277495508924e-06</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-8.8167121547009105e-07</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-0.00017788360939971246</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>9.4184221920893708e-05</v>
       </c>
     </row>
@@ -3292,1563 +3216,1563 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W1" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.76168099817727419</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>8.9897168564619928e-06</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-4.1233613793299839e-07</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>3.2550657974390578e-09</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>1.0356483217302747e-06</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>1.0662786550565437e-06</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>7.5566435578656718e-08</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>1.1221749942357141e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>-1.3413355869962233e-06</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-2.2098815846596395e-06</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-2.6955817294644343e-06</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-3.210570044584534e-06</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-1.1320723855292391e-07</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-2.7744535877728501e-07</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-4.90485310565251e-08</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>3.6732652335018156e-07</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-5.021024930920428e-07</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-3.3207235949000414e-08</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-4.9800027840162415e-07</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-3.0813850408224137e-07</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>3.2039835289092481e-06</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>-1.8571322945688978e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1">
         <v>0.018915501082125811</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-4.1233613793299839e-07</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>1.3702346644916692e-05</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-1.5713065141455744e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-1.1777359590922362e-06</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-2.2123489678599632e-05</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-1.2705844453958465e-07</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>1.1630254518017552e-07</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>4.0998625820181087e-05</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>6.4639388784477894e-05</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>7.238588123644637e-05</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>7.690623760539746e-05</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>3.6531998411135771e-06</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-1.0643350167643622e-06</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-1.7585091713064498e-06</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-3.6964016542596856e-09</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-6.826285598362719e-07</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-4.1112237301765609e-09</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-9.7882797935048713e-06</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>-3.0582548552636918e-06</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-0.0003771602230485129</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>0.00022008638798404957</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1">
         <v>-0.0001855575200024955</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>3.2550657974390578e-09</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-1.5713065141455744e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.8142653902620485e-09</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>5.4628280025685342e-08</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>2.9697172711335313e-07</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>4.5520739140051534e-10</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-2.3667263234212239e-09</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-4.7371718138394593e-07</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-7.4653189397900612e-07</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-8.3408861919929679e-07</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-8.8311074252317293e-07</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-4.2456507518035847e-08</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>1.2113973090079686e-08</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>1.9906067421481389e-08</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-2.1359631363752007e-10</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>7.1569058112326716e-09</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>2.3083203394596407e-13</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>1.1343385514355325e-07</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>3.5832271765346833e-08</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>4.3161750621055452e-06</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>-2.5406725155109557e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.010101910654716342</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1.0356483217302747e-06</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-1.1777359590922362e-06</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>5.4628280025685342e-08</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.00027157425716847831</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.00016676578292372117</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-5.9518935894524182e-06</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>-3.6353623766709025e-06</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-1.859845447754037e-05</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-3.0297127634582765e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-3.5517822839464065e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-3.3177809842393881e-05</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-3.7172074251915937e-06</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>7.8263475040726126e-07</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-1.0104683575536756e-06</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>5.5795321240917377e-07</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-6.1686836640139366e-07</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>1.7395814522335248e-08</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>4.7743504563851224e-06</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>1.9385231436120185e-06</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-1.7112033855291283e-05</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>-9.2902517769051632e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.059438930789790317</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>1.0662786550565437e-06</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-2.2123489678599632e-05</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>2.9697172711335313e-07</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.00016676578292372117</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0015913470434583458</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>-3.5069303368216958e-06</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-3.1511736380801216e-05</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-8.9825246384297948e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-0.00014456550850630787</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>-0.0001634562151311009</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-0.00016404393423273937</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-1.3449134659955681e-05</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>2.1407651507638737e-06</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>2.9958388816512993e-07</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>1.9727958634375753e-07</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>1.1653329240048021e-06</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-5.7929452708523553e-08</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>2.2172067080687485e-05</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>8.1985696933353817e-06</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>0.00058518789796719976</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>-0.00045449110293461093</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.0023506161432848352</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>7.5566435578656718e-08</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-1.2705844453958465e-07</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>4.5520739140051534e-10</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-5.9518935894524182e-06</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>-3.5069303368216958e-06</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>1.4161952580178026e-07</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>8.7979514688825425e-08</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>-1.2234452654561667e-07</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-1.5762027740149698e-07</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-1.0874944337111748e-07</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>-1.811741066722041e-07</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>2.8551442794247248e-08</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>3.5822843359808676e-09</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>4.3946629289300881e-08</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>3.9560483999008753e-09</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>5.1327449909232656e-08</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>8.4665786552717384e-10</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>1.856187716551186e-09</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>-2.0128991164275629e-08</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>4.3853740179789122e-06</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-6.7805315699619452e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.0022294423557952634</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1.1221749942357141e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>1.1630254518017552e-07</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-2.3667263234212239e-09</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>-3.6353623766709025e-06</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-3.1511736380801216e-05</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>8.7979514688825425e-08</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>6.7252829013262889e-07</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>8.057651752425921e-07</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>1.2942747031598898e-06</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>1.5381247485131361e-06</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>1.4730447813048125e-06</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>1.2745419157664018e-07</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-9.6044473195806603e-09</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>-3.3948733172322791e-09</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-1.4872814926291472e-08</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-6.6025087433297969e-09</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>3.3626002985084445e-09</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-2.0141486953954356e-07</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-1.0444502059334733e-07</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-2.9218237793675078e-06</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>3.0962566792038444e-06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.12306681555182976</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>-1.3413355869962233e-06</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>4.0998625820181087e-05</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-4.7371718138394593e-07</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-1.859845447754037e-05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-8.9825246384297948e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>-1.2234452654561667e-07</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>8.057651752425921e-07</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0016874431872579241</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.0016587193812321371</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.0016861460513263446</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.001698222906158882</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>1.3562380434868781e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-4.6808920325188816e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-6.784003256071851e-06</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-3.8008550549003028e-07</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-6.3722046410528768e-06</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>3.0959918257249499e-08</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-3.4930694217009974e-05</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-1.0776527679297108e-05</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>-0.0026065364182786821</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>0.00076584510235672956</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.14729337659903566</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-2.2098815846596395e-06</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>6.4639388784477894e-05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-7.4653189397900612e-07</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-3.0297127634582765e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-0.00014456550850630787</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>-1.5762027740149698e-07</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>1.2942747031598898e-06</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.0016587193812321371</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0018057567352503332</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0018329658923072378</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.0018523131171387466</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>2.0276754026758841e-05</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-6.9636819982960999e-06</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-1.0564633051679055e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>-7.3859438576306432e-07</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-8.4867799639489378e-06</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>1.9792370458016802e-08</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>-5.4734440780642354e-05</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>-1.6836608050158915e-05</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>-0.0032813827454564745</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.0012055954485307632</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.17464340762893132</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-2.6955817294644343e-06</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>7.238588123644637e-05</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-8.3408861919929679e-07</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-3.5517822839464065e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>-0.0001634562151311009</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-1.0874944337111748e-07</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>1.5381247485131361e-06</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.0016861460513263446</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0018329658923072378</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.0018892994463222525</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.0019065936015071993</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>2.2509396079420995e-05</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-7.8943952834166615e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-1.1818002906983493e-05</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-4.7000934026778777e-07</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-8.6691729964850753e-06</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-2.5674070928207243e-08</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-6.1192519715811585e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-1.9092258824691517e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-0.003504723625913708</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>0.0013507180497877773</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.1832399433158135</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-3.210570044584534e-06</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>7.690623760539746e-05</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-8.8311074252317293e-07</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-3.3177809842393881e-05</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-0.00016404393423273937</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>-1.811741066722041e-07</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1.4730447813048125e-06</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>0.001698222906158882</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.0018523131171387466</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.0019065936015071993</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.001953908682557395</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>2.4158653095237465e-05</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>-7.6631784070777744e-06</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-1.2254462042902807e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>2.876769071525483e-07</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-9.0451499595606575e-06</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-2.1850523864562213e-08</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-6.4193691194918643e-05</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-2.0319076841973915e-05</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>-0.0036343368982128879</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>0.0014162318121791763</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.0028785407128142869</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-1.1320723855292391e-07</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>3.6531998411135771e-06</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-4.2456507518035847e-08</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-3.7172074251915937e-06</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-1.3449134659955681e-05</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>2.8551442794247248e-08</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>1.2745419157664018e-07</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>1.3562380434868781e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>2.0276754026758841e-05</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>2.2509396079420995e-05</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>2.4158653095237465e-05</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>4.3540142681172344e-05</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>2.0244590781915906e-05</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>2.018199508042422e-05</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>2.0641199180034656e-05</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>4.4936898835126529e-07</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-4.4312549617852725e-08</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-3.1340245558441808e-06</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-1.2406886352261908e-06</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-0.00011926273704855542</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>6.6910088079812291e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.012404278961136026</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-2.7744535877728501e-07</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-1.0643350167643622e-06</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>1.2113973090079686e-08</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>7.8263475040726126e-07</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>2.1407651507638737e-06</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>3.5822843359808676e-09</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-9.6044473195806603e-09</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-4.6808920325188816e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-6.9636819982960999e-06</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-7.8943952834166615e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>-7.6631784070777744e-06</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>2.0244590781915906e-05</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>5.5998232150077328e-05</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>2.0787834616535527e-05</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>2.0620765473750303e-05</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>9.5857433080160728e-07</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-2.3679940424415806e-08</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>4.248148826935774e-07</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-1.2831879539216036e-08</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>1.4593919721218961e-05</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>-2.305061887778221e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.0024941073723350618</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-4.90485310565251e-08</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-1.7585091713064498e-06</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>1.9906067421481389e-08</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-1.0104683575536756e-06</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>2.9958388816512993e-07</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>4.3946629289300881e-08</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>-3.3948733172322791e-09</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-6.784003256071851e-06</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-1.0564633051679055e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-1.1818002906983493e-05</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-1.2254462042902807e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>2.018199508042422e-05</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>2.0787834616535527e-05</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>4.2774532138680126e-05</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>2.0641422712111748e-05</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>9.2084693350625649e-07</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-4.1688166099012291e-08</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>1.4564609716019888e-06</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>6.9053561131904491e-07</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>3.5940026615006827e-05</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-3.1747621952409672e-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.010502603500857773</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>3.6732652335018156e-07</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-3.6964016542596856e-09</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-2.1359631363752007e-10</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>5.5795321240917377e-07</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>1.9727958634375753e-07</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>3.9560483999008753e-09</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-1.4872814926291472e-08</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-3.8008550549003028e-07</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-7.3859438576306432e-07</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-4.7000934026778777e-07</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>2.876769071525483e-07</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>2.0641199180034656e-05</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>2.0620765473750303e-05</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>2.0641422712111748e-05</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>2.8963992856056444e-05</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>5.3213358222932529e-07</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>-3.2228650487551653e-08</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-3.9471729816155414e-07</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-3.0818520713700079e-07</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-1.6978504026389221e-05</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-6.322204655821695e-08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.096432330252303536</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-5.021024930920428e-07</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-6.826285598362719e-07</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>7.1569058112326716e-09</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-6.1686836640139366e-07</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>1.1653329240048021e-06</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>5.1327449909232656e-08</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-6.6025087433297969e-09</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-6.3722046410528768e-06</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-8.4867799639489378e-06</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-8.6691729964850753e-06</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-9.0451499595606575e-06</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>4.4936898835126529e-07</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>9.5857433080160728e-07</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>9.2084693350625649e-07</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>5.3213358222932529e-07</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>4.9692197939915894e-05</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>6.3845627767440012e-08</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>7.5923166161067883e-07</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-2.1810735607499794e-07</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>1.6644125912409681e-05</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-2.881697338289783e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.00090794447443789993</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-3.3207235949000414e-08</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-4.1112237301765609e-09</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>2.3083203394596407e-13</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>1.7395814522335248e-08</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-5.7929452708523553e-08</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>8.4665786552717384e-10</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>3.3626002985084445e-09</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>3.0959918257249499e-08</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>1.9792370458016802e-08</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-2.5674070928207243e-08</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-2.1850523864562213e-08</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-4.4312549617852725e-08</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-2.3679940424415806e-08</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-4.1688166099012291e-08</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>-3.2228650487551653e-08</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>6.3845627767440012e-08</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>2.2820655270761992e-08</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>-3.3443606681421174e-07</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-4.0930441903261583e-07</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-2.2192380087176416e-06</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-8.2893540115598041e-08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1">
         <v>-0.017288893239642007</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-4.9800027840162415e-07</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-9.7882797935048713e-06</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>1.1343385514355325e-07</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>4.7743504563851224e-06</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>2.2172067080687485e-05</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>1.856187716551186e-09</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-2.0141486953954356e-07</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-3.4930694217009974e-05</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>-5.4734440780642354e-05</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-6.1192519715811585e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-6.4193691194918643e-05</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-3.1340245558441808e-06</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>4.248148826935774e-07</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>1.4564609716019888e-06</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-3.9471729816155414e-07</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>7.5923166161067883e-07</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>-3.3443606681421174e-07</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>7.0600904319281549e-05</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>1.2794624458140551e-05</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>0.00031333815387945012</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.00018227425691741598</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.012724015892884789</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-3.0813850408224137e-07</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>-3.0582548552636918e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>3.5832271765346833e-08</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>1.9385231436120185e-06</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>8.1985696933353817e-06</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>-2.0128991164275629e-08</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-1.0444502059334733e-07</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-1.0776527679297108e-05</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>-1.6836608050158915e-05</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-1.9092258824691517e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-2.0319076841973915e-05</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-1.2406886352261908e-06</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-1.2831879539216036e-08</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>6.9053561131904491e-07</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-3.0818520713700079e-07</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-2.1810735607499794e-07</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-4.0930441903261583e-07</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>1.2794624458140551e-05</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>6.9675776214319463e-05</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>0.0001276754226497674</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-5.6175219457104599e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1">
         <v>-0.34350003540824209</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>3.2039835289092481e-06</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-0.0003771602230485129</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>4.3161750621055452e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-1.7112033855291283e-05</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>0.00058518789796719976</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>4.3853740179789122e-06</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-2.9218237793675078e-06</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>-0.0026065364182786821</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>-0.0032813827454564745</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-0.003504723625913708</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>-0.0036343368982128879</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-0.00011926273704855542</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>1.4593919721218961e-05</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>3.5940026615006827e-05</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-1.6978504026389221e-05</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>1.6644125912409681e-05</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-2.2192380087176416e-06</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>0.00031333815387945012</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>0.0001276754226497674</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.012221433936026285</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>-0.0062745016281929734</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1">
         <v>0.20819196092596209</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>-1.8571322945688978e-06</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>0.00022008638798404957</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>-2.5406725155109557e-06</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>-9.2902517769051632e-05</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>-0.00045449110293461093</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-6.7805315699619452e-07</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>3.0962566792038444e-06</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>0.00076584510235672956</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.0012055954485307632</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>0.0013507180497877773</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.0014162318121791763</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>6.6910088079812291e-05</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>-2.305061887778221e-05</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-3.1747621952409672e-05</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-6.322204655821695e-08</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-2.881697338289783e-05</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-8.2893540115598041e-08</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.00018227425691741598</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-5.6175219457104599e-05</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>-0.0062745016281929734</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.0040715310174582586</v>
       </c>
     </row>
@@ -4863,1563 +4787,1563 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W1" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.81470707945782184</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>8.3357445594536904e-06</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>-6.1451855683700792e-08</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>-4.2284197076001401e-10</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>1.0388861842181921e-06</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-4.9255667852415111e-07</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>5.4986257458599274e-08</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>1.2810924162374667e-07</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>8.523842583666966e-07</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>1.8595286394203471e-06</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>1.7438920924610892e-06</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>1.5078106730265329e-06</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>2.6451604557707702e-07</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-7.054017708213468e-07</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-9.097443045307694e-09</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>7.39850095640513e-07</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>1.1729451272028662e-06</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-4.5215908781874723e-08</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-7.6779737484988161e-07</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-1.4010657202954544e-07</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>-8.7080794577576244e-06</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>1.0403011214293117e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.0080518540059681468</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>-6.1451855683700792e-08</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>8.7903130353752859e-06</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-1.0268797409255787e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>1.3582589497328006e-05</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-3.6839062806763892e-06</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-3.0927041117708354e-07</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-8.065690659283723e-08</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>3.2644552982774014e-05</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>6.6689377178346754e-05</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>7.4393688686978001e-05</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>7.7175392823204567e-05</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>1.7744484139170356e-06</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-2.1638350834494372e-06</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-2.190961278400031e-06</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-5.9206410589576491e-07</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-1.6249101258775381e-06</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-1.6451227624543533e-08</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-6.0743329989765664e-06</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>1.0670450900438507e-06</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-0.00026665164775759715</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>0.00020816922652165594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.00011105244203922214</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>-4.2284197076001401e-10</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-1.0268797409255787e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.2230005788091293e-09</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>-8.4882325806318925e-08</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>1.2461456368667194e-07</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1.8288449923353351e-09</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-9.4597031878239238e-10</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-3.9407308453671973e-07</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-8.0508581290376512e-07</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>-8.9583228004649497e-07</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-9.2520465946623903e-07</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-2.1896481334792169e-08</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>2.5519340003313779e-08</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>2.5917525384478351e-08</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>6.9568032010787858e-09</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>1.7970128947751838e-08</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>1.6155875785185997e-10</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>7.4032260103684708e-08</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-1.2385415770915441e-08</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>3.1107668154018917e-06</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>-2.5119564257186626e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.029174092277506222</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1.0388861842181921e-06</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>1.3582589497328006e-05</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-8.4882325806318925e-08</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.00037917591442527323</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.00028098820317997119</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-8.3928859664449734e-06</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>-6.3890172855281048e-06</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>2.2710517107358362e-05</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>4.4204851993703512e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>4.6624748803042581e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>5.0768409855270286e-05</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-1.4015238625151449e-08</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-2.3394195584252868e-06</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>-2.4778734112545061e-06</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>2.7057686092045495e-07</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>-4.6360641799629267e-06</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>2.7615556214564088e-08</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>-2.6085320333234465e-06</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>1.0485672885678915e-06</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>-0.00049246759525847143</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>0.00014844795281781899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1">
         <v>0.01457140692318765</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-4.9255667852415111e-07</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-3.6839062806763892e-06</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>1.2461456368667194e-07</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.00028098820317997119</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0010516138565065242</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>-6.3095596049827413e-06</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>-2.1843683548989422e-05</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-6.2257910851657333e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-0.00013244727960713909</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>-0.00015077020048387131</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-0.00014960896307886527</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-9.1517593949755466e-06</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>1.7924761050505903e-06</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-1.3813153720954666e-06</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>2.0519098448157558e-06</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>2.1050815954055901e-06</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-2.0658628968715855e-08</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>1.4573699646210822e-05</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>3.1417169230494638e-07</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>9.1718300881729476e-05</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>-0.00039064411046105707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.00092232314794555258</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>5.4986257458599274e-08</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-3.0927041117708354e-07</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>1.8288449923353351e-09</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>-8.3928859664449734e-06</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>-6.3095596049827413e-06</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>2.0043833325605666e-07</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>1.5548281512875484e-07</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>-4.9407325636141788e-07</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-9.4697504387151113e-07</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-9.6093420284143338e-07</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>-1.0180214146219956e-06</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>-2.929610235631411e-08</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>4.5067628524930211e-08</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>3.5724623035214435e-08</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-2.6886508348101653e-09</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>1.6595079564806586e-07</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>2.4434588235728803e-10</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>4.1591452311127189e-08</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>-3.8737601988678384e-08</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>1.0609635283985636e-05</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-3.1584883450466392e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.0025911666911517628</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1.2810924162374667e-07</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-8.065690659283723e-08</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-9.4597031878239238e-10</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>-6.3890172855281048e-06</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-2.1843683548989422e-05</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>1.5548281512875484e-07</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>4.9804154619414776e-07</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>5.9324795182641709e-07</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>1.3679286692766367e-06</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>1.6446636051137268e-06</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>1.6281288155065322e-06</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>1.0688025414640981e-07</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-4.557981685739303e-09</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>1.8929165822577518e-08</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-6.7711824625585449e-08</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>3.0882598390341763e-08</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>2.3513240945221843e-09</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-1.9949075919043344e-07</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-4.742198507581257e-08</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>2.6639935387686535e-06</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>3.8764259251512434e-06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1">
         <v>-0.10923297163321088</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>8.523842583666966e-07</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>3.2644552982774014e-05</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-3.9407308453671973e-07</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>2.2710517107358362e-05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-6.2257910851657333e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>-4.9407325636141788e-07</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>5.9324795182641709e-07</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0015077025420630592</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0.0015381333158191353</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>0.0015763705215175539</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.0015842152740903862</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>9.291119389927079e-06</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-8.7679852464864119e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-1.0492423644327407e-05</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-3.2904914952889147e-06</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-1.3070573797347363e-05</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>-2.2522578910827188e-09</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-3.0453271310679341e-05</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>5.3902182903018492e-06</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>-0.0022920332446310816</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>0.00097895747156500961</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1">
         <v>-0.16582955027509089</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>1.8595286394203471e-06</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>6.6689377178346754e-05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-8.0508581290376512e-07</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>4.4204851993703512e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-0.00013244727960713909</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>-9.4697504387151113e-07</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>1.3679286692766367e-06</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>0.0015381333158191353</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0018909159504227452</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>0.0019477281045238281</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.0019640930716167352</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>1.7360062173117698e-05</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-1.9630606609330838e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>-2.1756746940694517e-05</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>-6.6778890797670941e-06</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>-2.5233696689282037e-05</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>-1.2254850256065099e-07</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>-5.9406151161812993e-05</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>1.0444237857165567e-05</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>-0.0033973374690490898</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.0020031993322742305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.17247290126795628</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>1.7438920924610892e-06</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>7.4393688686978001e-05</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>-8.9583228004649497e-07</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>4.6624748803042581e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>-0.00015077020048387131</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-9.6093420284143338e-07</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>1.6446636051137268e-06</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>0.0015763705215175539</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.0019477281045238281</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.002047088104815591</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.0020598976516946399</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>1.93525837608026e-05</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-2.1553754218901324e-05</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-2.3746938173719995e-05</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-6.583236924055332e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-2.7478383966365037e-05</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-1.9413445059266292e-07</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-6.650625348448132e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>1.1456886841913535e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-0.0036569935167001539</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>0.0022464851612368541</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1">
         <v>-0.17227056815531591</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1.5078106730265329e-06</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>7.7175392823204567e-05</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-9.2520465946623903e-07</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>5.0768409855270286e-05</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-0.00014960896307886527</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>-1.0180214146219956e-06</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1.6281288155065322e-06</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>0.0015842152740903862</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.0019640930716167352</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.0020598976516946399</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0021055220329910802</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>1.9866228867335507e-05</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>-2.1813218948460446e-05</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-2.4443308340360768e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-6.4281810711885972e-06</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-2.8559419599885133e-05</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-1.9264204606200251e-07</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-6.7945117947183434e-05</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>1.1842733596172781e-05</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>-0.0037447873616341882</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>0.0022965850769531659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1">
         <v>-0.0084789053683691582</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>2.6451604557707702e-07</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>1.7744484139170356e-06</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-2.1896481334792169e-08</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-1.4015238625151449e-08</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-9.1517593949755466e-06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>-2.929610235631411e-08</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>1.0688025414640981e-07</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>9.291119389927079e-06</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>1.7360062173117698e-05</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>1.93525837608026e-05</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>1.9866228867335507e-05</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>5.3755232347895911e-05</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>2.547723088121306e-05</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>2.5576975948749432e-05</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>2.5899854216011806e-05</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>5.4467441476124417e-07</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-4.8968628812263688e-08</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-2.0569254469832201e-06</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-2.6050234444053672e-07</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-7.7097280763720823e-05</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>5.2594547101762479e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.018541080337433995</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-7.054017708213468e-07</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-2.1638350834494372e-06</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>2.5519340003313779e-08</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>-2.3394195584252868e-06</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>1.7924761050505903e-06</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>4.5067628524930211e-08</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-4.557981685739303e-09</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-8.7679852464864119e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-1.9630606609330838e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-2.1553754218901324e-05</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>-2.1813218948460446e-05</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>2.547723088121306e-05</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>7.0689432766375267e-05</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>2.6675000922131909e-05</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>2.6110525957758915e-05</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>2.4227641284440594e-06</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-2.7356431637945603e-08</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>1.0773926202666527e-06</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-1.1386170399844736e-06</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>4.8492871631901607e-05</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>-6.4360427817911699e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.0030576894212899284</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-9.097443045307694e-09</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-2.190961278400031e-06</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>2.5917525384478351e-08</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>-2.4778734112545061e-06</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-1.3813153720954666e-06</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>3.5724623035214435e-08</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>1.8929165822577518e-08</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-1.0492423644327407e-05</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>-2.1756746940694517e-05</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-2.3746938173719995e-05</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-2.4443308340360768e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>2.5576975948749432e-05</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>2.6675000922131909e-05</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>5.3243880578565691e-05</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>2.620446105453689e-05</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>2.5751474669502297e-06</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>-4.3313426130191924e-08</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>1.6108744212372107e-06</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-2.4127502292066938e-07</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>5.2140365974336975e-05</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-6.2955636632969089e-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1">
         <v>-0.021658855641052317</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>7.39850095640513e-07</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-5.9206410589576491e-07</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>6.9568032010787858e-09</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>2.7057686092045495e-07</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>2.0519098448157558e-06</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-2.6886508348101653e-09</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-6.7711824625585449e-08</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-3.2904914952889147e-06</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-6.6778890797670941e-06</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-6.583236924055332e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-6.4281810711885972e-06</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>2.5899854216011806e-05</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>2.6110525957758915e-05</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>2.620446105453689e-05</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>3.6775206616964287e-05</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>8.8264225035025932e-07</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>-3.8858333118754767e-08</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-1.639419877370714e-07</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>-7.7573884584518867e-07</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-2.9104770677777938e-06</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-1.5606092370354891e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.094711865434932443</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>1.1729451272028662e-06</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-1.6249101258775381e-06</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>1.7970128947751838e-08</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>-4.6360641799629267e-06</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>2.1050815954055901e-06</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>1.6595079564806586e-07</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>3.0882598390341763e-08</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-1.3070573797347363e-05</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>-2.5233696689282037e-05</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-2.7478383966365037e-05</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-2.8559419599885133e-05</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>5.4467441476124417e-07</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>2.4227641284440594e-06</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>2.5751474669502297e-06</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>8.8264225035025932e-07</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.00015232040267536319</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>7.7053251699558958e-08</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>1.6621719265294163e-06</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>-1.0936274130855395e-06</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>5.4958060058173574e-05</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-9.3320294196593906e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.00095882611463690703</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-4.5215908781874723e-08</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-1.6451227624543533e-08</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>1.6155875785185997e-10</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>2.7615556214564088e-08</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-2.0658628968715855e-08</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>2.4434588235728803e-10</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>2.3513240945221843e-09</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>-2.2522578910827188e-09</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>-1.2254850256065099e-07</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-1.9413445059266292e-07</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-1.9264204606200251e-07</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-4.8968628812263688e-08</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-2.7356431637945603e-08</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>-4.3313426130191924e-08</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>-3.8858333118754767e-08</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>7.7053251699558958e-08</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>2.5507839753399835e-08</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>-3.6735714723050514e-07</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-4.6804906386253895e-07</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-2.0532749627590431e-06</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-5.8327367138644585e-07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.0018394293112592983</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-7.6779737484988161e-07</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-6.0743329989765664e-06</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>7.4032260103684708e-08</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>-2.6085320333234465e-06</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>1.4573699646210822e-05</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>4.1591452311127189e-08</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-1.9949075919043344e-07</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-3.0453271310679341e-05</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>-5.9406151161812993e-05</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-6.650625348448132e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-6.7945117947183434e-05</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-2.0569254469832201e-06</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>1.0773926202666527e-06</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>1.6108744212372107e-06</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-1.639419877370714e-07</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>1.6621719265294163e-06</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>-3.6735714723050514e-07</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>8.4146600324762086e-05</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>1.1301558345793732e-05</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>0.00023451746222461137</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.00018161738719069541</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.013503068342401472</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-1.4010657202954544e-07</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>1.0670450900438507e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-1.2385415770915441e-08</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>1.0485672885678915e-06</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>3.1417169230494638e-07</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>-3.8737601988678384e-08</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-4.742198507581257e-08</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>5.3902182903018492e-06</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>1.0444237857165567e-05</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>1.1456886841913535e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>1.1842733596172781e-05</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-2.6050234444053672e-07</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-1.1386170399844736e-06</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-2.4127502292066938e-07</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>-7.7573884584518867e-07</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>-1.0936274130855395e-06</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-4.6804906386253895e-07</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>1.1301558345793732e-05</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>8.6314683528040159e-05</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>1.0495932751067299e-05</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>3.2390436747226831e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.58401054056574941</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>-8.7080794577576244e-06</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-0.00026665164775759715</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>3.1107668154018917e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>-0.00049246759525847143</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>9.1718300881729476e-05</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>1.0609635283985636e-05</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>2.6639935387686535e-06</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>-0.0022920332446310816</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>-0.0033973374690490898</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-0.0036569935167001539</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>-0.0037447873616341882</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-7.7097280763720823e-05</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>4.8492871631901607e-05</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>5.2140365974336975e-05</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-2.9104770677777938e-06</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>5.4958060058173574e-05</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-2.0532749627590431e-06</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>0.00023451746222461137</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>1.0495932751067299e-05</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.0098660891699510582</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>-0.0067580393677340962</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1">
         <v>-0.51925497394550302</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>1.0403011214293117e-05</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>0.00020816922652165594</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>-2.5119564257186626e-06</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0.00014844795281781899</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>-0.00039064411046105707</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-3.1584883450466392e-06</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>3.8764259251512434e-06</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>0.00097895747156500961</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.0020031993322742305</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>0.0022464851612368541</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.0022965850769531659</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>5.2594547101762479e-05</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>-6.4360427817911699e-05</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-6.2955636632969089e-05</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-1.5606092370354891e-05</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-9.3320294196593906e-05</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-5.8327367138644585e-07</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.00018161738719069541</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>3.2390436747226831e-05</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>-0.0067580393677340962</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.0062151411964118525</v>
       </c>
     </row>
